--- a/2026/PICHINCHA/Abril/PICHINCHA-Abril.xlsx
+++ b/2026/PICHINCHA/Abril/PICHINCHA-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PICHINCHA\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PICHINCHA\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54095451-4358-40C4-B283-FA9E8A46467B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1666E0-418C-46F0-898D-0877EB7FDE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -22,11 +22,16 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="81">
   <si>
     <t>UF</t>
   </si>
@@ -238,18 +243,12 @@
     <t>SEGURO DE VIDA. SRA MONICA GOROSITO</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>SUBIDOS EN EN3R0</t>
   </si>
   <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
-    <t>DOARTERO JULIO - CAMBIO DE DOS AUTOMATICOS - MATERIALES Y MANO DE OBRA</t>
-  </si>
-  <si>
     <t>Vto. 15/05</t>
   </si>
   <si>
@@ -259,10 +258,22 @@
     <t>ABRIL</t>
   </si>
   <si>
-    <t>METROGAS</t>
-  </si>
-  <si>
-    <t>FLOW</t>
+    <t xml:space="preserve">FLOW </t>
+  </si>
+  <si>
+    <t>AYSA VTO MES DE AGOSTO 2025</t>
+  </si>
+  <si>
+    <t>AYSA CARGO POR AVISO DE MORA</t>
+  </si>
+  <si>
+    <t>METROGAS VTO 17/03</t>
+  </si>
+  <si>
+    <t>METROGAS VTO 17/04</t>
+  </si>
+  <si>
+    <t>SEBASTIAN</t>
   </si>
 </sst>
 </file>
@@ -275,7 +286,7 @@
     <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,13 +395,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1099,7 +1103,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1311,18 +1315,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1380,11 +1379,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1463,9 +1458,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1503,9 +1498,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1538,9 +1533,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1573,9 +1585,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1753,22 +1782,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1776,27 +1805,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1804,13 +1833,13 @@
       <c r="C7" s="67"/>
       <c r="D7" s="67"/>
       <c r="E7" s="24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F7" s="109" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1818,30 +1847,30 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="120"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="127" t="s">
+      <c r="E11" s="128" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="127"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F11" s="128"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B12" s="50"/>
-      <c r="C12" s="150">
-        <v>81064.320000000007</v>
+      <c r="C12" s="149">
+        <v>21891.25</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="55" t="s">
@@ -1851,168 +1880,168 @@
         <v>-94900.571369267185</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>64</v>
       </c>
       <c r="B13" s="50"/>
-      <c r="C13" s="150">
-        <v>20951.11</v>
+      <c r="C13" s="149">
+        <v>20891.55</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="154"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="121" t="s">
+      <c r="E13" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="127">
+        <f>'prorrateo '!F10</f>
+        <v>399048.98800000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="C14" s="149">
+        <v>15666.16</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="127">
+        <f>-(C37)</f>
+        <v>-687632.45000000007</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="121" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="122"/>
-      <c r="C14" s="150">
+      <c r="B15" s="122"/>
+      <c r="C15" s="149">
         <v>119977</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="58">
-        <f>'prorrateo '!F10</f>
-        <v>337233.93055999995</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="121" t="s">
+      <c r="D15" s="42"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="58"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="152">
+      <c r="B16" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="79">
         <v>42700</v>
-      </c>
-      <c r="D15" s="5"/>
-      <c r="E15" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="58">
-        <f>-(C37)</f>
-        <v>-741661.92</v>
-      </c>
-      <c r="H15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="121" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16" s="50"/>
-      <c r="C16" s="152">
-        <v>64351.88</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="57"/>
       <c r="F16" s="58"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="121" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="122"/>
-      <c r="C17" s="151">
-        <v>24175.95</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="B17" s="50"/>
+      <c r="C17" s="79">
+        <v>164351.88</v>
+      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="57"/>
       <c r="F17" s="58"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="121" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B18" s="122"/>
-      <c r="C18" s="151">
-        <v>95246.25</v>
-      </c>
-      <c r="D18" s="5"/>
+      <c r="C18" s="117">
+        <v>24175.95</v>
+      </c>
       <c r="E18" s="57"/>
       <c r="F18" s="58"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="121" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B19" s="122"/>
-      <c r="C19" s="151">
-        <v>86842.66</v>
-      </c>
+      <c r="C19" s="117">
+        <v>95246.25</v>
+      </c>
+      <c r="D19" s="5"/>
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
-      <c r="H19" s="106"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="123"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="86">
-        <f>SUM(C12:C19)</f>
-        <v>535309.17000000004</v>
-      </c>
-      <c r="E20" s="59" t="s">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="121" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="122"/>
+      <c r="C20" s="117">
+        <v>86842.66</v>
+      </c>
+      <c r="E20" s="57"/>
+      <c r="F20" s="58"/>
+      <c r="H20" s="106"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="123"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="86">
+        <f>SUM(C12:C20)</f>
+        <v>591742.70000000007</v>
+      </c>
+      <c r="E21" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="119">
-        <f>SUM(F12:F19)</f>
-        <v>-499328.56080926728</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="125" t="s">
+      <c r="F21" s="119">
+        <f>SUM(F12:F20)</f>
+        <v>-383484.03336926724</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="20"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="121" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="126"/>
-      <c r="C22" s="117">
-        <v>71833</v>
-      </c>
+      <c r="B22" s="122"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="5"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="121" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B23" s="126"/>
-      <c r="C23" s="151">
-        <v>4519.75</v>
+      <c r="C23" s="117">
+        <v>91370</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="129" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" s="130"/>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="121" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="126"/>
       <c r="C24" s="117">
-        <v>130000</v>
+        <v>4519.75</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B25" s="34"/>
       <c r="C25" s="110"/>
@@ -2020,32 +2049,32 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="32"/>
       <c r="B26" s="33"/>
       <c r="C26" s="107">
-        <f>SUM(C21:C25)</f>
-        <v>206352.75</v>
+        <f>SUM(C22:C25)</f>
+        <v>95889.75</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="54"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="46" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="47"/>
       <c r="C27" s="48">
-        <f>+C26+C20</f>
-        <v>741661.92</v>
+        <f>+C26+C21</f>
+        <v>687632.45000000007</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="68" t="s">
         <v>24</v>
       </c>
@@ -2054,18 +2083,18 @@
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="43"/>
       <c r="B30" s="29"/>
       <c r="C30" s="53"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="51"/>
       <c r="B31" s="50"/>
       <c r="C31" s="52">
@@ -2073,7 +2102,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="61"/>
       <c r="C32" s="52">
@@ -2081,19 +2110,19 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="77"/>
       <c r="B33" s="78"/>
       <c r="C33" s="80"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="77"/>
       <c r="B34" s="84"/>
       <c r="C34" s="85"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="77"/>
       <c r="B35" s="83"/>
       <c r="C35" s="80">
@@ -2101,7 +2130,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="62" t="s">
         <v>23</v>
       </c>
@@ -2111,107 +2140,106 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>54</v>
       </c>
       <c r="C37" s="52">
         <f>C27-C25</f>
-        <v>741661.92</v>
+        <v>687632.45000000007</v>
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C38" s="76">
         <f>+C27</f>
-        <v>741661.92</v>
+        <v>687632.45000000007</v>
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="62" t="s">
         <v>13</v>
       </c>
       <c r="B39" s="63"/>
       <c r="C39" s="64">
         <f>+C27+C36</f>
-        <v>741661.92</v>
+        <v>687632.45000000007</v>
       </c>
       <c r="E39" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="128"/>
-      <c r="C46" s="128"/>
-      <c r="D46" s="128"/>
-      <c r="E46" s="128"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="128"/>
-      <c r="C47" s="128"/>
-      <c r="D47" s="128"/>
-      <c r="E47" s="128"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B48" s="128"/>
-      <c r="C48" s="128"/>
-      <c r="D48" s="128"/>
-      <c r="E48" s="128"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="129"/>
+      <c r="C46" s="129"/>
+      <c r="D46" s="129"/>
+      <c r="E46" s="129"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="129"/>
+      <c r="C47" s="129"/>
+      <c r="D47" s="129"/>
+      <c r="E47" s="129"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="129"/>
+      <c r="C48" s="129"/>
+      <c r="D48" s="129"/>
+      <c r="E48" s="129"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
       <c r="B60" s="18"/>
       <c r="C60" s="20"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="B46:E48"/>
-    <mergeCell ref="A24:B24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2229,25 +2257,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" customWidth="1"/>
-    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="21"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="104" t="s">
         <v>55</v>
       </c>
@@ -2263,12 +2291,12 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
       <c r="K1" s="70">
-        <v>398812.47</v>
+        <v>687632.45000000007</v>
       </c>
       <c r="L1" s="70"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ABRIL</v>
@@ -2288,7 +2316,7 @@
       <c r="L2" s="112"/>
       <c r="M2" s="75"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2329,7 +2357,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2363,7 +2391,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2375,23 +2403,25 @@
       </c>
       <c r="D5" s="17"/>
       <c r="E5" s="40">
-        <v>110932.21399999999</v>
-      </c>
-      <c r="F5" s="79"/>
+        <v>195131.99656</v>
+      </c>
+      <c r="F5" s="79">
+        <v>79762</v>
+      </c>
       <c r="G5" s="66">
         <f>E5-F5</f>
-        <v>110932.21399999999</v>
+        <v>115369.99656</v>
       </c>
       <c r="H5" s="69">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>4437.28856</v>
+        <v>4614.7998624000002</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
       </c>
       <c r="J5" s="37">
         <f>K$1/5</f>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="K5" s="115">
         <f>K2*D5</f>
@@ -2399,14 +2429,14 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>195131.99656</v>
+        <v>257511.28642240001</v>
       </c>
       <c r="M5" s="38">
         <f>L5*4%+L5</f>
-        <v>202937.2764224</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>267811.73787929601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2418,15 +2448,14 @@
       </c>
       <c r="D6" s="17"/>
       <c r="E6" s="40">
-        <v>115369.50255999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="F6" s="79">
-        <f>E6</f>
-        <v>115369.50255999999</v>
+        <v>80000</v>
       </c>
       <c r="G6" s="66">
         <f>E6-F6</f>
-        <v>0</v>
+        <v>-237.5060000000085</v>
       </c>
       <c r="H6" s="69">
         <f t="shared" ref="H6:H9" si="0">IF(G6&gt;0,G6*4%,0)</f>
@@ -2437,7 +2466,7 @@
       </c>
       <c r="J6" s="37">
         <f t="shared" ref="J6:J9" si="1">K$1/5</f>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="K6" s="115">
         <f>K2*D6</f>
@@ -2445,14 +2474,14 @@
       </c>
       <c r="L6" s="15">
         <f>J6+K6+H6+G6</f>
-        <v>79762.493999999992</v>
+        <v>137288.984</v>
       </c>
       <c r="M6" s="38">
         <f t="shared" ref="M6:M9" si="2">L6*4%+L6</f>
-        <v>82952.993759999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <v>142780.54336000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2464,23 +2493,25 @@
       </c>
       <c r="D7" s="17"/>
       <c r="E7" s="40">
-        <v>110932.21399999999</v>
-      </c>
-      <c r="F7" s="79"/>
+        <v>195131.99656</v>
+      </c>
+      <c r="F7" s="79">
+        <v>79762</v>
+      </c>
       <c r="G7" s="66">
         <f t="shared" ref="G7:G8" si="3">E7-F7</f>
-        <v>110932.21399999999</v>
+        <v>115369.99656</v>
       </c>
       <c r="H7" s="69">
         <f t="shared" si="0"/>
-        <v>4437.28856</v>
+        <v>4614.7998624000002</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
       </c>
       <c r="J7" s="37">
         <f t="shared" si="1"/>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="K7" s="115">
         <f>K2*D7</f>
@@ -2488,14 +2519,14 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>195131.99656</v>
+        <v>257511.28642240001</v>
       </c>
       <c r="M7" s="38">
         <f t="shared" si="2"/>
-        <v>202937.2764224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+        <v>267811.73787929601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2503,15 +2534,15 @@
         <v>4</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D8" s="17"/>
       <c r="E8" s="40">
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="F8" s="79">
         <f>E8</f>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="G8" s="66">
         <f t="shared" si="3"/>
@@ -2526,7 +2557,7 @@
       </c>
       <c r="J8" s="37">
         <f t="shared" si="1"/>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="K8" s="115">
         <f>K2*D8</f>
@@ -2534,14 +2565,14 @@
       </c>
       <c r="L8" s="15">
         <f>J8+K8+H8+G8</f>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="M8" s="38">
         <f t="shared" si="2"/>
-        <v>82952.993759999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+        <v>143027.54960000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2553,11 +2584,11 @@
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="40">
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="F9" s="79">
         <f>E9</f>
-        <v>110932.21399999999</v>
+        <v>79762.493999999992</v>
       </c>
       <c r="G9" s="66">
         <f>E9-F9</f>
@@ -2572,7 +2603,7 @@
       </c>
       <c r="J9" s="37">
         <f t="shared" si="1"/>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="K9" s="115">
         <f>K2*D9</f>
@@ -2580,14 +2611,14 @@
       </c>
       <c r="L9" s="15">
         <f>J9+K9+H9+G9</f>
-        <v>79762.493999999992</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="M9" s="38">
         <f t="shared" si="2"/>
-        <v>82952.993759999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>143027.54960000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2599,19 +2630,19 @@
       </c>
       <c r="E10" s="41">
         <f t="shared" si="4"/>
-        <v>559098.35855999996</v>
+        <v>629551.47511999996</v>
       </c>
       <c r="F10" s="41">
         <f>SUM(F5:F9)</f>
-        <v>337233.93055999995</v>
+        <v>399048.98800000001</v>
       </c>
       <c r="G10" s="49">
         <f t="shared" si="4"/>
-        <v>221864.42799999999</v>
+        <v>230502.48712000001</v>
       </c>
       <c r="H10" s="49">
         <f t="shared" si="4"/>
-        <v>8874.5771199999999</v>
+        <v>9229.5997248000003</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="4"/>
@@ -2619,7 +2650,7 @@
       </c>
       <c r="J10" s="45">
         <f t="shared" si="4"/>
-        <v>398812.47</v>
+        <v>687632.45000000007</v>
       </c>
       <c r="K10" s="45">
         <f t="shared" si="4"/>
@@ -2627,78 +2658,78 @@
       </c>
       <c r="L10" s="116">
         <f t="shared" si="4"/>
-        <v>629551.47511999996</v>
+        <v>927364.53684479999</v>
       </c>
       <c r="M10" s="116">
         <f t="shared" si="4"/>
-        <v>654733.5341248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="131"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="131"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>964459.11831859208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="132"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="132"/>
-      <c r="K16" s="132"/>
-      <c r="L16" s="132"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="131"/>
+      <c r="F13" s="131"/>
+      <c r="G13" s="131"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="131"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="131"/>
+      <c r="J15" s="131"/>
+      <c r="K15" s="131"/>
+      <c r="L15" s="131"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="131"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="131"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2714,68 +2745,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="138" t="s">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="140"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="139"/>
       <c r="F1" s="87"/>
       <c r="G1" s="87"/>
     </row>
-    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="141" t="s">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="140" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="144">
+      <c r="B2" s="141"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="143">
         <v>565</v>
       </c>
-      <c r="E2" s="145"/>
+      <c r="E2" s="144"/>
       <c r="F2" s="88"/>
       <c r="G2" s="88"/>
     </row>
-    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="146" t="s">
+    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="145" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="146" t="s">
+      <c r="C3" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="148" t="s">
+      <c r="D3" s="147" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="133" t="s">
+      <c r="E3" s="132" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="133" t="s">
+      <c r="F3" s="132" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="133" t="s">
+      <c r="G3" s="132" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="147"/>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-    </row>
-    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="146"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="133"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="89">
         <v>1</v>
       </c>
@@ -2798,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="89">
         <v>2</v>
       </c>
@@ -2821,7 +2852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="89">
         <v>3</v>
       </c>
@@ -2844,7 +2875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="89">
         <v>4</v>
       </c>
@@ -2867,7 +2898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="89">
         <v>5</v>
       </c>
@@ -2890,7 +2921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="94">
         <v>6</v>
       </c>
@@ -2913,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="99" t="s">
         <v>8</v>
       </c>
@@ -2932,12 +2963,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="135"/>
-      <c r="B12" s="136"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="137"/>
+    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="134"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="136"/>
       <c r="F12" s="87"/>
       <c r="G12" s="87"/>
     </row>

--- a/2026/PICHINCHA/Abril/PICHINCHA-Abril.xlsx
+++ b/2026/PICHINCHA/Abril/PICHINCHA-Abril.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PICHINCHA\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1666E0-418C-46F0-898D-0877EB7FDE5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C2D046-48F9-47E6-9101-F8BCA5FA6D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="82">
   <si>
     <t>UF</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>SEBASTIAN</t>
+  </si>
+  <si>
+    <t>Recuperacion de intereses por pago fuera de termino a administracion - Desde enero 25 a dia de la fecha - Debido a que la caja inicial pertenece a la administracion</t>
   </si>
 </sst>
 </file>
@@ -452,7 +455,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1095,6 +1098,17 @@
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1103,7 +1117,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1316,6 +1330,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1379,7 +1394,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1859,17 +1879,17 @@
       <c r="B11" s="29"/>
       <c r="C11" s="120"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="128" t="s">
+      <c r="E11" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="128"/>
+      <c r="F11" s="129"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>76</v>
       </c>
       <c r="B12" s="50"/>
-      <c r="C12" s="149">
+      <c r="C12" s="128">
         <v>21891.25</v>
       </c>
       <c r="D12" s="5"/>
@@ -1885,7 +1905,7 @@
         <v>64</v>
       </c>
       <c r="B13" s="50"/>
-      <c r="C13" s="149">
+      <c r="C13" s="128">
         <v>20891.55</v>
       </c>
       <c r="D13" s="5"/>
@@ -1902,7 +1922,7 @@
         <v>77</v>
       </c>
       <c r="B14" s="50"/>
-      <c r="C14" s="149">
+      <c r="C14" s="128">
         <v>15666.16</v>
       </c>
       <c r="D14" s="5"/>
@@ -1914,17 +1934,21 @@
         <v>-687632.45000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="121" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="122"/>
-      <c r="C15" s="149">
+      <c r="C15" s="128">
         <v>119977</v>
       </c>
       <c r="D15" s="42"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="58"/>
+      <c r="E15" s="150" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="151">
+        <v>-98883.56</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="121" t="s">
@@ -1937,8 +1961,8 @@
         <v>42700</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="58"/>
+      <c r="E16" s="150"/>
+      <c r="F16" s="151"/>
       <c r="H16" t="s">
         <v>70</v>
       </c>
@@ -1952,8 +1976,8 @@
         <v>164351.88</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="58"/>
+      <c r="E17" s="150"/>
+      <c r="F17" s="151"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="121" t="s">
@@ -2002,7 +2026,7 @@
       </c>
       <c r="F21" s="119">
         <f>SUM(F12:F20)</f>
-        <v>-383484.03336926724</v>
+        <v>-482367.59336926724</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2179,22 +2203,22 @@
       <c r="E45" s="16"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="129"/>
-      <c r="C46" s="129"/>
-      <c r="D46" s="129"/>
-      <c r="E46" s="129"/>
+      <c r="B46" s="130"/>
+      <c r="C46" s="130"/>
+      <c r="D46" s="130"/>
+      <c r="E46" s="130"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="129"/>
-      <c r="C47" s="129"/>
-      <c r="D47" s="129"/>
-      <c r="E47" s="129"/>
+      <c r="B47" s="130"/>
+      <c r="C47" s="130"/>
+      <c r="D47" s="130"/>
+      <c r="E47" s="130"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="129"/>
-      <c r="C48" s="129"/>
-      <c r="D48" s="129"/>
-      <c r="E48" s="129"/>
+      <c r="B48" s="130"/>
+      <c r="C48" s="130"/>
+      <c r="D48" s="130"/>
+      <c r="E48" s="130"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="19"/>
@@ -2237,9 +2261,11 @@
       <c r="C67" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="B46:E48"/>
+    <mergeCell ref="E15:E17"/>
+    <mergeCell ref="F15:F17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2666,70 +2692,70 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="130"/>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="131"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
     </row>
     <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M12" s="6"/>
     </row>
     <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
+      <c r="C13" s="132"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="132"/>
+      <c r="J13" s="132"/>
+      <c r="K13" s="132"/>
+      <c r="L13" s="132"/>
     </row>
     <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
-      <c r="F14" s="131"/>
-      <c r="G14" s="131"/>
-      <c r="H14" s="131"/>
-      <c r="I14" s="131"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="131"/>
-      <c r="L14" s="131"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="132"/>
+      <c r="F14" s="132"/>
+      <c r="G14" s="132"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="132"/>
+      <c r="J14" s="132"/>
+      <c r="K14" s="132"/>
+      <c r="L14" s="132"/>
     </row>
     <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="131"/>
-      <c r="D15" s="131"/>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="131"/>
-      <c r="H15" s="131"/>
-      <c r="I15" s="131"/>
-      <c r="J15" s="131"/>
-      <c r="K15" s="131"/>
-      <c r="L15" s="131"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="132"/>
     </row>
     <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="131"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="131"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="131"/>
+      <c r="C16" s="132"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="132"/>
+      <c r="F16" s="132"/>
+      <c r="G16" s="132"/>
+      <c r="H16" s="132"/>
+      <c r="I16" s="132"/>
+      <c r="J16" s="132"/>
+      <c r="K16" s="132"/>
+      <c r="L16" s="132"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2751,60 +2777,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="138"/>
-      <c r="C1" s="138"/>
-      <c r="D1" s="138"/>
-      <c r="E1" s="139"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="140"/>
       <c r="F1" s="87"/>
       <c r="G1" s="87"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="140" t="s">
+      <c r="A2" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="141"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="143">
+      <c r="B2" s="142"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="144">
         <v>565</v>
       </c>
-      <c r="E2" s="144"/>
+      <c r="E2" s="145"/>
       <c r="F2" s="88"/>
       <c r="G2" s="88"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="145" t="s">
+      <c r="A3" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="146" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="145" t="s">
+      <c r="C3" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="147" t="s">
+      <c r="D3" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="132" t="s">
+      <c r="E3" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="132" t="s">
+      <c r="F3" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="132" t="s">
+      <c r="G3" s="133" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="146"/>
-      <c r="B4" s="146"/>
-      <c r="C4" s="146"/>
-      <c r="D4" s="148"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
+      <c r="A4" s="147"/>
+      <c r="B4" s="147"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="149"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="89">
@@ -2964,11 +2990,11 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="134"/>
-      <c r="B12" s="135"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="136"/>
+      <c r="A12" s="135"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="137"/>
       <c r="F12" s="87"/>
       <c r="G12" s="87"/>
     </row>

--- a/2026/PICHINCHA/Abril/PICHINCHA-Abril.xlsx
+++ b/2026/PICHINCHA/Abril/PICHINCHA-Abril.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\PICHINCHA\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PICHINCHA\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C2D046-48F9-47E6-9101-F8BCA5FA6D2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35072ED5-A373-490F-9E4F-DE8117074389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -22,11 +22,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$10</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1337,6 +1332,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1393,12 +1394,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1478,9 +1473,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1518,9 +1513,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1553,26 +1548,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1605,26 +1583,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1802,22 +1763,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" customWidth="1"/>
+    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>18</v>
       </c>
@@ -1825,27 +1786,27 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="23"/>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D6" s="29"/>
       <c r="E6" s="29"/>
       <c r="F6" s="29"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>58</v>
       </c>
@@ -1859,7 +1820,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1867,12 +1828,12 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
         <v>10</v>
       </c>
@@ -1884,7 +1845,7 @@
       </c>
       <c r="F11" s="129"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="51" t="s">
         <v>76</v>
       </c>
@@ -1900,7 +1861,7 @@
         <v>-94900.571369267185</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="51" t="s">
         <v>64</v>
       </c>
@@ -1914,10 +1875,10 @@
       </c>
       <c r="F13" s="127">
         <f>'prorrateo '!F10</f>
-        <v>399048.98800000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>629788.98111999989</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="51" t="s">
         <v>77</v>
       </c>
@@ -1934,7 +1895,7 @@
         <v>-687632.45000000007</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="121" t="s">
         <v>45</v>
       </c>
@@ -1943,14 +1904,14 @@
         <v>119977</v>
       </c>
       <c r="D15" s="42"/>
-      <c r="E15" s="150" t="s">
+      <c r="E15" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="151">
+      <c r="F15" s="132">
         <v>-98883.56</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="121" t="s">
         <v>19</v>
       </c>
@@ -1961,13 +1922,13 @@
         <v>42700</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="151"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="132"/>
       <c r="H16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="121" t="s">
         <v>75</v>
       </c>
@@ -1976,10 +1937,10 @@
         <v>164351.88</v>
       </c>
       <c r="D17" s="5"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="151"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E17" s="131"/>
+      <c r="F17" s="132"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="121" t="s">
         <v>68</v>
       </c>
@@ -1990,7 +1951,7 @@
       <c r="E18" s="57"/>
       <c r="F18" s="58"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="121" t="s">
         <v>78</v>
       </c>
@@ -2002,7 +1963,7 @@
       <c r="E19" s="57"/>
       <c r="F19" s="58"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="121" t="s">
         <v>79</v>
       </c>
@@ -2014,7 +1975,7 @@
       <c r="F20" s="58"/>
       <c r="H20" s="106"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="123"/>
       <c r="B21" s="124"/>
       <c r="C21" s="86">
@@ -2026,10 +1987,10 @@
       </c>
       <c r="F21" s="119">
         <f>SUM(F12:F20)</f>
-        <v>-482367.59336926724</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>-251627.60024926736</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="125" t="s">
         <v>21</v>
       </c>
@@ -2039,7 +2000,7 @@
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="121" t="s">
         <v>63</v>
       </c>
@@ -2051,7 +2012,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="121" t="s">
         <v>69</v>
       </c>
@@ -2063,7 +2024,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="31" t="s">
         <v>71</v>
       </c>
@@ -2073,7 +2034,7 @@
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="32"/>
       <c r="B26" s="33"/>
       <c r="C26" s="107">
@@ -2085,7 +2046,7 @@
       <c r="F26" s="54"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="46" t="s">
         <v>12</v>
       </c>
@@ -2098,7 +2059,7 @@
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="68" t="s">
         <v>24</v>
       </c>
@@ -2107,18 +2068,18 @@
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="43"/>
       <c r="B30" s="29"/>
       <c r="C30" s="53"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="51"/>
       <c r="B31" s="50"/>
       <c r="C31" s="52">
@@ -2126,7 +2087,7 @@
       </c>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="60"/>
       <c r="B32" s="61"/>
       <c r="C32" s="52">
@@ -2134,19 +2095,19 @@
       </c>
       <c r="F32" s="6"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="77"/>
       <c r="B33" s="78"/>
       <c r="C33" s="80"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="77"/>
       <c r="B34" s="84"/>
       <c r="C34" s="85"/>
       <c r="F34" s="6"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="77"/>
       <c r="B35" s="83"/>
       <c r="C35" s="80">
@@ -2154,7 +2115,7 @@
       </c>
       <c r="F35" s="6"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="62" t="s">
         <v>23</v>
       </c>
@@ -2164,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -2174,7 +2135,7 @@
       </c>
       <c r="F37" s="6"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>49</v>
       </c>
@@ -2184,7 +2145,7 @@
       </c>
       <c r="F38" s="6"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="62" t="s">
         <v>13</v>
       </c>
@@ -2195,67 +2156,67 @@
       </c>
       <c r="E39" s="16"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B46" s="130"/>
       <c r="C46" s="130"/>
       <c r="D46" s="130"/>
       <c r="E46" s="130"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B47" s="130"/>
       <c r="C47" s="130"/>
       <c r="D47" s="130"/>
       <c r="E47" s="130"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B48" s="130"/>
       <c r="C48" s="130"/>
       <c r="D48" s="130"/>
       <c r="E48" s="130"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="19"/>
       <c r="B60" s="18"/>
       <c r="C60" s="20"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="18"/>
       <c r="B61" s="18"/>
       <c r="C61" s="18"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="18"/>
       <c r="B62" s="18"/>
       <c r="C62" s="18"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="18"/>
       <c r="B63" s="18"/>
       <c r="C63" s="18"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="18"/>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="18"/>
       <c r="B65" s="18"/>
       <c r="C65" s="18"/>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="18"/>
       <c r="B66" s="18"/>
       <c r="C66" s="18"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="18"/>
       <c r="B67" s="18"/>
       <c r="C67" s="18"/>
@@ -2283,25 +2244,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="0.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="17.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="21"/>
+    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="0.109375" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="17.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="104" t="s">
         <v>55</v>
       </c>
@@ -2322,7 +2283,7 @@
       <c r="L1" s="70"/>
       <c r="M1" s="27"/>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="71" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de ABRIL</v>
@@ -2342,7 +2303,7 @@
       <c r="L2" s="112"/>
       <c r="M2" s="75"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2383,7 +2344,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -2417,7 +2378,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>1</v>
       </c>
@@ -2432,15 +2393,16 @@
         <v>195131.99656</v>
       </c>
       <c r="F5" s="79">
-        <v>79762</v>
+        <f>E5</f>
+        <v>195131.99656</v>
       </c>
       <c r="G5" s="66">
         <f>E5-F5</f>
-        <v>115369.99656</v>
+        <v>0</v>
       </c>
       <c r="H5" s="69">
         <f>IF(G5&gt;0,G5*4%,0)</f>
-        <v>4614.7998624000002</v>
+        <v>0</v>
       </c>
       <c r="I5" s="15">
         <v>0</v>
@@ -2455,14 +2417,14 @@
       </c>
       <c r="L5" s="15">
         <f>J5+K5+H5+G5</f>
-        <v>257511.28642240001</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="M5" s="38">
         <f>L5*4%+L5</f>
-        <v>267811.73787929601</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>143027.54960000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>2</v>
       </c>
@@ -2507,7 +2469,7 @@
         <v>142780.54336000001</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="12">
         <v>3</v>
       </c>
@@ -2522,15 +2484,16 @@
         <v>195131.99656</v>
       </c>
       <c r="F7" s="79">
-        <v>79762</v>
+        <f>E7</f>
+        <v>195131.99656</v>
       </c>
       <c r="G7" s="66">
         <f t="shared" ref="G7:G8" si="3">E7-F7</f>
-        <v>115369.99656</v>
+        <v>0</v>
       </c>
       <c r="H7" s="69">
         <f t="shared" si="0"/>
-        <v>4614.7998624000002</v>
+        <v>0</v>
       </c>
       <c r="I7" s="15">
         <v>0</v>
@@ -2545,14 +2508,14 @@
       </c>
       <c r="L7" s="15">
         <f>J7+K7+H7+G7</f>
-        <v>257511.28642240001</v>
+        <v>137526.49000000002</v>
       </c>
       <c r="M7" s="38">
         <f t="shared" si="2"/>
-        <v>267811.73787929601</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>143027.54960000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="12">
         <v>4</v>
       </c>
@@ -2598,7 +2561,7 @@
         <v>143027.54960000003</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="12">
         <v>5</v>
       </c>
@@ -2644,7 +2607,7 @@
         <v>143027.54960000003</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>8</v>
       </c>
@@ -2660,15 +2623,15 @@
       </c>
       <c r="F10" s="41">
         <f>SUM(F5:F9)</f>
-        <v>399048.98800000001</v>
+        <v>629788.98111999989</v>
       </c>
       <c r="G10" s="49">
         <f t="shared" si="4"/>
-        <v>230502.48712000001</v>
+        <v>-237.5060000000085</v>
       </c>
       <c r="H10" s="49">
         <f t="shared" si="4"/>
-        <v>9229.5997248000003</v>
+        <v>0</v>
       </c>
       <c r="I10" s="11">
         <f t="shared" si="4"/>
@@ -2684,78 +2647,78 @@
       </c>
       <c r="L10" s="116">
         <f t="shared" si="4"/>
-        <v>927364.53684479999</v>
+        <v>687394.94400000002</v>
       </c>
       <c r="M10" s="116">
         <f t="shared" si="4"/>
-        <v>964459.11831859208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="131"/>
-      <c r="B11" s="131"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131"/>
-      <c r="E11" s="131"/>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="131"/>
-      <c r="J11" s="131"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="131"/>
-      <c r="M11" s="131"/>
-    </row>
-    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>714890.74176000012</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="51.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="133"/>
+      <c r="B11" s="133"/>
+      <c r="C11" s="133"/>
+      <c r="D11" s="133"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="133"/>
+      <c r="G11" s="133"/>
+      <c r="H11" s="133"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="133"/>
+      <c r="M11" s="133"/>
+    </row>
+    <row r="12" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M12" s="6"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
-      <c r="H13" s="132"/>
-      <c r="I13" s="132"/>
-      <c r="J13" s="132"/>
-      <c r="K13" s="132"/>
-      <c r="L13" s="132"/>
-    </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
-      <c r="H14" s="132"/>
-      <c r="I14" s="132"/>
-      <c r="J14" s="132"/>
-      <c r="K14" s="132"/>
-      <c r="L14" s="132"/>
-    </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
-      <c r="H15" s="132"/>
-      <c r="I15" s="132"/>
-      <c r="J15" s="132"/>
-      <c r="K15" s="132"/>
-      <c r="L15" s="132"/>
-    </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
-      <c r="H16" s="132"/>
-      <c r="I16" s="132"/>
-      <c r="J16" s="132"/>
-      <c r="K16" s="132"/>
-      <c r="L16" s="132"/>
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="134"/>
+      <c r="D13" s="134"/>
+      <c r="E13" s="134"/>
+      <c r="F13" s="134"/>
+      <c r="G13" s="134"/>
+      <c r="H13" s="134"/>
+      <c r="I13" s="134"/>
+      <c r="J13" s="134"/>
+      <c r="K13" s="134"/>
+      <c r="L13" s="134"/>
+    </row>
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="134"/>
+      <c r="D14" s="134"/>
+      <c r="E14" s="134"/>
+      <c r="F14" s="134"/>
+      <c r="G14" s="134"/>
+      <c r="H14" s="134"/>
+      <c r="I14" s="134"/>
+      <c r="J14" s="134"/>
+      <c r="K14" s="134"/>
+      <c r="L14" s="134"/>
+    </row>
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="134"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="134"/>
+    </row>
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="134"/>
+      <c r="D16" s="134"/>
+      <c r="E16" s="134"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="134"/>
+      <c r="H16" s="134"/>
+      <c r="I16" s="134"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="134"/>
+      <c r="L16" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2771,68 +2734,68 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="138" t="s">
+    <row r="1" spans="1:7" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="142"/>
       <c r="F1" s="87"/>
       <c r="G1" s="87"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="141" t="s">
+    <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="143" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="142"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="144">
+      <c r="B2" s="144"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="146">
         <v>565</v>
       </c>
-      <c r="E2" s="145"/>
+      <c r="E2" s="147"/>
       <c r="F2" s="88"/>
       <c r="G2" s="88"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="146" t="s">
+    <row r="3" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="146" t="s">
+      <c r="C3" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="148" t="s">
+      <c r="D3" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="133" t="s">
+      <c r="E3" s="135" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="133" t="s">
+      <c r="F3" s="135" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="133" t="s">
+      <c r="G3" s="135" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="147"/>
-      <c r="B4" s="147"/>
-      <c r="C4" s="147"/>
-      <c r="D4" s="149"/>
-      <c r="E4" s="134"/>
-      <c r="F4" s="134"/>
-      <c r="G4" s="134"/>
-    </row>
-    <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="149"/>
+      <c r="B4" s="149"/>
+      <c r="C4" s="149"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="136"/>
+      <c r="F4" s="136"/>
+      <c r="G4" s="136"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="89">
         <v>1</v>
       </c>
@@ -2855,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="89">
         <v>2</v>
       </c>
@@ -2878,7 +2841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="89">
         <v>3</v>
       </c>
@@ -2901,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="89">
         <v>4</v>
       </c>
@@ -2924,7 +2887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="89">
         <v>5</v>
       </c>
@@ -2947,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="94">
         <v>6</v>
       </c>
@@ -2970,7 +2933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="99" t="s">
         <v>8</v>
       </c>
@@ -2989,12 +2952,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="135"/>
-      <c r="B12" s="136"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="137"/>
+    <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="137"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="139"/>
       <c r="F12" s="87"/>
       <c r="G12" s="87"/>
     </row>
